--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/DEFENSORES DE GLEW 2.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/DEFENSORES DE GLEW 2.xlsx
@@ -398,803 +398,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>899160</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>914400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="1 Imagen" descr="VICTOR CARPIO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="3002280"/>
-          <a:ext cx="899160" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="2 Imagen" descr="DARIO GURLEKIAN.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="3924300"/>
-          <a:ext cx="876300" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>906780</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="3 Imagen" descr="JHONATAN AGUIRRE.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="5737860"/>
-          <a:ext cx="906780" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>891540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="4 Imagen" descr="NICO AMBROSETTI.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="7551420"/>
-          <a:ext cx="952500" cy="891540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1043940</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="5 Imagen" descr="RODRIGO YANTZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10599420" y="8450580"/>
-          <a:ext cx="1036320" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1043940</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="6 Imagen" descr="RUBEN OTAROLA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="9349740"/>
-          <a:ext cx="1043940" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>982980</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="7 Imagen" descr="SANTIAGO ANTUNEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="12992100"/>
-          <a:ext cx="982980" cy="906780"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1036320</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="8 Imagen" descr="BRIAN FARIÑA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="13891260"/>
-          <a:ext cx="1036320" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1051560</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="9 Imagen" descr="NAHUEL DOMINGUEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="14790420"/>
-          <a:ext cx="1051560" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="10 Imagen" descr="DUSTIN BLANCO}.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="15712440"/>
-          <a:ext cx="1066800" cy="929640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>883920</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="11 Imagen" descr="PROFE WALTER.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="17731740"/>
-          <a:ext cx="1028700" cy="883920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="12 Imagen" descr="PROFE GUSTAVO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="18638520"/>
-          <a:ext cx="1066800" cy="960120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>906780</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>883920</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="13 Imagen" descr="NICOLAS PAZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="4846320"/>
-          <a:ext cx="906780" cy="883920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>929640</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="14 Imagen" descr="ESTEBAN SPERA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="6652260"/>
-          <a:ext cx="929640" cy="906780"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1043940</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="15 Imagen" descr="ROBERTO DAMIAN BATILANA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="10256520"/>
-          <a:ext cx="1043940" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1051560</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="16 Imagen" descr="LUCA POYO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="11170920"/>
-          <a:ext cx="1051560" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="17 Imagen" descr="MARCELO AZCONA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="12077700"/>
-          <a:ext cx="1066800" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1059180</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="18 Imagen" descr="GUSTAVO FLORENTIN.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10591800" y="16626840"/>
-          <a:ext cx="1059180" cy="929640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
